--- a/resources/templates/maintenance-annual-template.xlsx
+++ b/resources/templates/maintenance-annual-template.xlsx
@@ -3060,8 +3060,7 @@
       </c>
     </row>
     <row r="29" spans="1:30" s="21" customFormat="1" ht="22.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37">
-        <v>2</v>
+      <c r="A29">
       </c>
       <c r="B29" s="23" t="s">
         <v>64</v>

--- a/resources/templates/maintenance-annual-template.xlsx
+++ b/resources/templates/maintenance-annual-template.xlsx
@@ -43,7 +43,7 @@
     <t>_________________________</t>
   </si>
   <si>
-    <t>А.А.Королев</t>
+    <t/>
   </si>
   <si>
     <t>ГОДОВОЙ ГРАФИК</t>
@@ -216,7 +216,7 @@
     <t>Начальник КЦ</t>
   </si>
   <si>
-    <t>М.И.Малашкеевич</t>
+    <t/>
   </si>
   <si>
     <t>СОГЛАСОВАНО</t>
